--- a/extracted/reports/tramos_filtrado_estricto/tramo_243+700_243+730.xlsx
+++ b/extracted/reports/tramos_filtrado_estricto/tramo_243+700_243+730.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Filtro estricto: INICIO (KM) y FIN (KM) contenidos en el tramo | Total registros: 15</t>
+          <t>Filtro: FIN completo contenido en tramo; FIN en blanco si INICIO cae en tramo | Total registros: 23</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Año 2020 (1 registros)</t>
+          <t>Año 2019 (1 registros)</t>
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
@@ -610,7 +610,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Reposición de Señalización Vertical T2</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -620,27 +620,23 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
+          <t>2019-10-29</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>243+706</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>243+720</t>
-        </is>
-      </c>
+          <t>243+725</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n">
-        <v>54</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Año 2021 (2 registros)</t>
+          <t>Año 2020 (1 registros)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -684,121 +680,121 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>Limpieza de carril/pista y bermas T2</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>243+706</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>243+720</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Año 2021 (2 registros)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Limpieza Residuos Solidos / Basuras</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>2021-06-17</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>243+700</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>243+720</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>80</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Reparación de Bache Superficial T2</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>243+700</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>243+720</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Año 2022 (2 registros)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Reparación de Bache Superficial T2</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2022-11-05</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -808,85 +804,81 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>243+710</t>
+          <t>243+720</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>10</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Reposición de Cuneta</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>243+700</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>243+710</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>3</v>
-      </c>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Año 2022 (3 registros)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Año 2023 (1 registros)</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Reposición de Señalización Vertical T2</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>2022-01-27</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>243+730</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n">
+        <v>0.5625</v>
       </c>
     </row>
     <row r="20">
@@ -902,7 +894,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2022-11-05</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -912,101 +904,101 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>243+720</t>
+          <t>243+710</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Año 2024 (4 registros)</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Reposición de Cuneta</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>243+700</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>243+710</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Año 2023 (2 registros)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>INICIO (KM)</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>FIN (KM)</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>METRADO</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Remocion de Derrumbes T2</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>2024-03-11</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>243+700</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>243+730</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>120</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1016,17 +1008,17 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>243+730</t>
+          <t>243+720</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Repintado de Postes de (hitos) kilométricos T2</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1036,111 +1028,107 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
+          <t>243+729</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Año 2024 (6 registros)</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Remocion de Derrumbes T2</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
           <t>243+700</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>243+730</t>
         </is>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F28" s="5" t="n">
         <v>120</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza de Parapetos Veredas de Concreto T2</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>243+705</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>243+730</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Año 2025 (4 registros)</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1150,57 +1138,53 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>243+720</t>
+          <t>243+730</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Juntas en Cunetas y Bermas</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>243+700</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>243+720</t>
-        </is>
-      </c>
+          <t>243+701</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n">
-        <v>11.33333333333333</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Cajas de Inspección Subdren T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1210,53 +1194,367 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>243+720</t>
+          <t>243+730</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>Limpieza de Parapetos Veredas de Concreto T2</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>243+705</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>243+730</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Placas de Señalización Vertical T2</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>243+720</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Año 2025 (6 registros)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
           <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>2025-01-08</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>243+700</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>243+700</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>243+720</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Juntas en Cunetas y Bermas</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>243+700</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>243+720</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>11.33333333333333</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Cajas de Inspección Subdren T2</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>243+700</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>243+720</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de carril/pista y bermas T2</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>2025-09-13</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>243+700</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>243+720</t>
         </is>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F40" s="5" t="n">
         <v>800</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Cajas de Inspección Subdren T2</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>243+700</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Año 2026 (1 registros)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Reposición de Delineador T2</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>243+700</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
